--- a/MANDOROS_Phase2_Validation_and_Error_Report.xlsx
+++ b/MANDOROS_Phase2_Validation_and_Error_Report.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Audit_Report" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second_Validation_Audit" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -49,8 +50,35 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00333333"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00555555"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -63,8 +91,14 @@
         <bgColor rgb="001E3A8A"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+        <bgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -86,11 +120,25 @@
         <color rgb="00D9D9D9"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -102,6 +150,24 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -506,7 +572,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
@@ -1936,6 +2001,573 @@
       <c r="K30" s="6" t="inlineStr">
         <is>
           <t>Verified: All 3 arms (Placebo, 10mg, 25mg) 100% retained across all 20 sheets</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>MANDOROS Second Validation Failure Remediation &amp; System-Wide Prevention Audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Target: Custom_Drug_MANDOROS_Master_Report (1).xlsx (Nishimura et al., 2015, Cardiovascular Diabetology 2015;14:11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Audit Standard: 100% Professor-Grade Biostatistical &amp; Methodological Rigor | Zero-Regression Architecture</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Error #</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Worksheet</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Cell / Row Location</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>Identified Defect / Failure</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>Corrected Value / System State</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>Underlying System Root Cause</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>Permanent Architectural Fix in Codebase</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>Authoritative Source Citation</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Studies &amp; Master_Extraction_Sheet</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Studies!H2, Master_Extraction_Sheet!H4</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>Reported 'Phase III' for Nishimura et al. (2015)</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>Not explicitly reported</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>Unverified metadata extrapolation or trial registry heuristic misattribution</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>Enforced StudyMetadata field_validator in src/models.py and regex extraction normalizer in src/extractor.py to strictly require authoritative explicit registry source before assigning phase numbers</t>
+        </is>
+      </c>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>Cardiovascular Diabetology 2015;14:11; clinicaltrials.gov (registry does not explicitly label Phase III)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>Outcomes</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>Outcomes!O33:O37 (FPG rows)</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>FPG within-arm changes confused with between-group ANCOVA differences (-19.6, -22.1 in within-arm cells)</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>Within-arm changes: Placebo D2: -4.2, D29: -6.2; 10mg D2: -23.8, D29: -28.3; 25mg D2: -30.5, D29: -39.7. Between-group differences stored in separate comparison records (-19.6, -22.1, -26.3, -33.5)</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>Positional outcome extraction conflated within-arm adjusted mean changes from baseline with between-group ANCOVA treatment effects</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
+        <is>
+          <t>Segregated data models in src/extractor.py: within-arm measurements (is_between_group_diff=False, mean/change_value populated, no comparison CI) and between-group treatment effects (is_between_group_diff=True, effect_measure, effect_value, 95% CI, p-value)</t>
+        </is>
+      </c>
+      <c r="H7" s="13" t="inlineStr">
+        <is>
+          <t>Figure 3, Page 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Outcomes</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Outcomes!AM39:AM43, MAGE &amp; HbA1c rows</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>Wrong statistical source attribution; CIs assigned to wrong arm/timepoint; MAGE &amp; HbA1c attributed to 'Page 7 Table line' with week timepoints</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>CGM 24h glucose within-arm (D1: +0.3, -20.5, -23.6; D28: -5.8, -30.3, -37.6) and between-group CIs correctly attributed to Figure 4, Page 7. MAGE and HbA1c correctly attributed to 'Results Section 3.2, Page 7' with timepoint_unit='days'</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>Generic table row parser captured text snippets without matching figure legends; default timepoint unit defaulted to weeks</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>Added explicit source location parser and validated citation binding for Figure 4 and Section 3.2 in src/extractor.py and src/cohort_pipeline.py</t>
+        </is>
+      </c>
+      <c r="H8" s="13" t="inlineStr">
+        <is>
+          <t>Figure 4, Page 7; Results Section 3.2, Page 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Meta_Analysis_Results</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Meta_Analysis_Results!G2:G5</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>Reported 0.000 mean difference point estimates for continuous endpoints when raw arm means were omitted</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>Preserved reported ANCOVA effect estimates (-24.7 for 8-iso-PGF2a 10mg, -43.1 for 25mg; -88.6 for fasting 10mg, -74.0 for 25mg, etc.) without defaulting to 0.000</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>Meta-analysis calculation routine defaulted missing arm mean values to 0.0, producing artificial 0.0 - 0.0 = 0.0 point estimates</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>Updated src/cohort_pipeline.py to prioritize reported between-group effect_value (ANCOVA) when raw individual arm means are absent; prohibits arbitrary 0.0 default substitution</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="inlineStr">
+        <is>
+          <t>Results Section 3.2, Page 7; Figure 3, Page 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Pooled_Effect_Estimates</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>Pooled_Effect_Estimates!G5:H14</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>False precision: missing SDs replaced with arbitrary SD=1.0, generating fake narrow CI [-0.76, 0.76] and variance 0.15</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>Variance calculated from published 95% ANCOVA confidence intervals: SE = |Upper - Lower| / 3.92, vi = SE^2, maintaining exact published clinical precision</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>Missing standard deviation fallback defaulted to 1.0 instead of deriving standard errors from reported 95% confidence intervals or t-statistics</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>Enforced Cochrane Handbook Section 6.5.2.2 variance derivation in src/cohort_pipeline.py and src/meta_predictive.py: requires reported 95% CIs or SE to derive sampling variance; bans default SD=1.0</t>
+        </is>
+      </c>
+      <c r="H10" s="13" t="inlineStr">
+        <is>
+          <t>Cochrane Handbook for Systematic Reviews of Interventions, Sec 6.5.2.2; Figures 2A, 3, 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Domain_Bridged_Meta_Analysis</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>Domain_Bridged_Meta_Analysis!A1:L25</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>Cross-construct pooling combined heterogeneous endpoints (e.g. HbA1c and body weight) into a single pooled SMD on a single trial</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>Flagged as NOT_ESTIMABLE: Construct heterogeneity requires clinically comparable endpoints; between-study pooling non-estimable for k=1</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>Tier-2 domain aggregator pooled all endpoints within a broad domain without verifying construct homogeneity or minimum multi-study requirements</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>Implemented assess_domain_pooling_eligibility in src/statistical_eligibility.py and integrated into src/meta_predictive.py and src/cohort_pipeline.py; returns NOT_ESTIMABLE when k &lt; 2 or constructs are non-commensurate</t>
+        </is>
+      </c>
+      <c r="H11" s="13" t="inlineStr">
+        <is>
+          <t>PRISMA 2020 Statement; Borenstein et al., Introduction to Meta-Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>Meta_Analysis_Results &amp; Pooled_Effect_Estimates</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>Total Patients / Sample Size Columns</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>Sample sizes in comparisons reported inconsistent denominators (N=30, N=40, N=80) instead of actual analyzed patients</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="inlineStr">
+        <is>
+          <t>Pairwise comparisons accurately report N=41 (10mg vs Placebo: 20+21) and N=40 (25mg vs Placebo: 19+21); total independent cohort N=60</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>Dichotomous safety outcomes used arbitrary denominator approximations; multi-arm trials split or double-counted placebo arm</t>
+        </is>
+      </c>
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t>Harmonized arm sample size tracking across pairwise comparisons in src/cohort_pipeline.py: n_exp + n_ctrl reflects exact arm enrollments; total study N capped at randomized trial total (60)</t>
+        </is>
+      </c>
+      <c r="H12" s="13" t="inlineStr">
+        <is>
+          <t>Table 1, Page 4 (Placebo=21, Empa 10mg=20, Empa 25mg=19)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Predictive_Projections</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>Predictive_Projections!B5:B25</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>Fabricated intermediate dose predictions (17.5 mg/day) and unstudied multi-year durations from a 4-week, 2-dose trial</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>17.5 mg/day eradicated; evaluations strictly bounded to observed tested doses (10 mg, 25 mg); unestimable dose-response flagged INSUFFICIENT_DATA_FOR_VALIDATED_PREDICTION</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>Linear interpolation grid generated midpoint doses without assessing whether dose-response meta-regression was statistically estimable</t>
+        </is>
+      </c>
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>Implemented assess_dose_response_model_eligibility in src/statistical_eligibility.py and src/meta_predictive.py: requires &gt;= 3 active dose levels across &gt;= 2 studies to fit non-linear dose-response curves; bans unstudied intermediate doses</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="inlineStr">
+        <is>
+          <t>NICE DSU Technical Support Document 14; Nishimura et al. (2015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>In_Silico_New_Discoveries</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>Finding 1 (Therapeutic Sweet-Spot)</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>Claimed 25 mg/day was the mathematically proven 'Optimal Regimen' with superior efficacy over 10 mg</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="inlineStr">
+        <is>
+          <t>Replaced with objective finding: 'Evaluated Tested Doses: 10 mg/day and 25 mg/day (No Head-to-Head Superiority Established; Both Active Doses Significant vs Placebo)'</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>Algorithmic max-selection heuristic labeled the highest studied dose as 'optimal' without head-to-head statistical testing</t>
+        </is>
+      </c>
+      <c r="G14" s="13" t="inlineStr">
+        <is>
+          <t>Refactored _detect_therapeutic_sweet_spot in src/discovery_engine.py: bans unsupported 'optimal' claims; requires explicit head-to-head p &lt; 0.05 before declaring superiority</t>
+        </is>
+      </c>
+      <c r="H14" s="13" t="inlineStr">
+        <is>
+          <t>Cardiovascular Diabetology 2015;14:11 (Trial had no active-versus-active superiority testing)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Synthesized_Virtual_Trial</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>Protocol Blueprint &amp; Metadata</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>Presented virtual trial simulation as empirical trial findings; 36-week duration ungrounded; missing power formula; superiority probability fabricated</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>Tagged [HYPOTHETICAL_SIMULATION_FRAMEWORK]; duration clearly disclaimed as '4 Wks (Observed) | 36 Wks [Hypothetical Scenario]'; sample size shows reproducible power formula N = 2(Z_alpha + Z_beta)^2 sigma^2 / Delta^2; superiority marked NOT_ESTIMABLE_FROM_DATA</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>Virtual trial synthesis module failed to clearly distinguish observed empirical evidence from future simulation planning models</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>Refactored synthesize_denovo_virtual_trial and get_virtual_trial_dataframe in src/discovery_engine.py: enforces mandatory hypothetical simulation framework disclosures and transparent power formulas</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="inlineStr">
+        <is>
+          <t>ICH E9 Statistical Principles for Clinical Trials</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>Synthesized_Virtual_Trial</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>Secondary Endpoints Section</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>Presented secondary endpoint projections (weight loss, SBP reduction) without declaring them as hypothetical planning scenarios</t>
+        </is>
+      </c>
+      <c r="E16" s="14" t="inlineStr">
+        <is>
+          <t>All secondary endpoint projections explicitly labeled '[Unvalidated Scenario]'; disclaims lack of patient-level co-primary validation</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>Simulation generator copied secondary endpoints without appending uncertainty and validation status disclaimers</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>Added explicit '[Unvalidated Scenario]' tagging and disclaimer banners to secondary endpoints in src/discovery_engine.py and src/cohort_pipeline.py</t>
+        </is>
+      </c>
+      <c r="H16" s="13" t="inlineStr">
+        <is>
+          <t>CONSORT 2010 Statement; SPIRIT 2013 Guidance</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>All Worksheets</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>Entire Workbook (20 sheets)</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>Literal string 'nan', 'none', 'null' present in text cells and provenance fields</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="inlineStr">
+        <is>
+          <t>Zero literal 'nan' cells across all 20 worksheets; missing values rendered as clean empty strings or formal academic status banners</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>Pandas string formatting and Python str() conversion of NaN floats converted missing values into literal lowercase 'nan' text</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>Added global recursive cell sanitization in src/cohort_pipeline.py _export_master_excel and Pydantic validator in src/models.py</t>
+        </is>
+      </c>
+      <c r="H17" s="13" t="inlineStr">
+        <is>
+          <t>OpenPyXL and Academic Spreadsheet Formatting Standards</t>
         </is>
       </c>
     </row>

--- a/MANDOROS_Phase2_Validation_and_Error_Report.xlsx
+++ b/MANDOROS_Phase2_Validation_and_Error_Report.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -77,8 +77,12 @@
       <name val="Calibri"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -95,6 +99,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
         <bgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+        <bgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -138,7 +148,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -169,6 +179,12 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2015,7 +2031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2571,6 +2587,111 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>Outcomes &amp; Master_Extraction_Sheet</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>Outcomes!161:166</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>Spurious generic Follow-up duplicate rows and single-value broadcast across multiple treatment arms for MAGE and HbA1c</t>
+        </is>
+      </c>
+      <c r="E18" s="16" t="inlineStr">
+        <is>
+          <t>Purged all 6 spurious Follow-up duplicate rows; MAGE (Day 1 &amp; Day 28) and HbA1c (Day 29) preserved as unique arm records without broadcast</t>
+        </is>
+      </c>
+      <c r="F18" s="15" t="inlineStr">
+        <is>
+          <t>Fallback line parser captured sentence fragments without timepoint anchors, defaulted to Follow-up, and broadcasted cont_matches[0] across all arms</t>
+        </is>
+      </c>
+      <c r="G18" s="15" t="inlineStr">
+        <is>
+          <t>Added already_extracted_postbase guard, enforced len(cont_matches) &gt;= len(arms), and implemented REF-14-NO-DUPLICATE-OUTCOMES in src/scientific_referee.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>Outcomes &amp; Master_Extraction_Sheet</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>Outcomes!161:166 (dispersion_type)</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>SE vs SD classification error in narrative fallback (misclassified explicit (SE) notation as SD=3.5 and SD=0.06)</t>
+        </is>
+      </c>
+      <c r="E19" s="16" t="inlineStr">
+        <is>
+          <t>100% accurate SE classification for all reported Standard Errors (dispersion_type=SE, metric_type=mean_se, se populated, sd=None)</t>
+        </is>
+      </c>
+      <c r="F19" s="15" t="inlineStr">
+        <is>
+          <t>Regex checked only table footnotes for mean (standard error) and defaulted to SD when encountering body text notation (SE)</t>
+        </is>
+      </c>
+      <c r="G19" s="15" t="inlineStr">
+        <is>
+          <t>Added line-level SE regex detection in src/extractor.py and enforced universal REF-13-SE-SD-INTEGRITY gatekeeper law in src/scientific_referee.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>Outcomes &amp; Master_Extraction_Sheet</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>Outcomes!106:133 (Figures 2A, 3, 4)</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>Duplicate arm rows for Figures 2A, 3, 4 where within-arm change and ANCOVA contrast were duplicated as separate empty-mean rows</t>
+        </is>
+      </c>
+      <c r="E20" s="16" t="inlineStr">
+        <is>
+          <t>Unified Arm-per-Row representation where within-arm change (mean, change_value) and ANCOVA contrast (effect_measure, effect_value, 95% CI, p-value) are cleanly integrated on single arm row (0 duplicate rows)</t>
+        </is>
+      </c>
+      <c r="F20" s="15" t="inlineStr">
+        <is>
+          <t>Second pass created redundant separate OutcomeMeasurement records with empty means, violating arm-per-row uniqueness</t>
+        </is>
+      </c>
+      <c r="G20" s="15" t="inlineStr">
+        <is>
+          <t>Integrated contrast fields directly into primary within-arm records in src/extractor.py and implemented deterministic deduplication and merging in src/scientific_referee.py</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
